--- a/data/system.xlsx
+++ b/data/system.xlsx
@@ -3,7 +3,7 @@
 <s:workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:s="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <s:workbookPr codeName="ThisWorkbook"/>
   <s:bookViews>
-    <s:workbookView activeTab="2"/>
+    <s:workbookView activeTab="1"/>
   </s:bookViews>
   <s:sheets>
     <s:sheet name="ORGGUID" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="82">
   <si>
     <t>case_id</t>
   </si>
@@ -120,15 +120,6 @@
     <t>{"QueryType": "checkUserPhone", "Params": '{"PHONE":"#USERPHONE#","ORGGUID": "#ORGGUID#", "AppName": "com.romens.health.pharmacy.client"}'}</t>
   </si>
   <si>
-    <t>App验证手机号-手机号为空</t>
-  </si>
-  <si>
-    <t>{"QueryType": "checkUserPhone", "Params": '{"PHONE":"","ORGGUID": "#ORGGUID#", "AppName": "com.romens.health.pharmacy.client"}'}</t>
-  </si>
-  <si>
-    <t>未通过</t>
-  </si>
-  <si>
     <t>App验证手机号-QueryType为空</t>
   </si>
   <si>
@@ -151,12 +142,6 @@
   </si>
   <si>
     <t>{"QueryType": "checkUserPhone"}</t>
-  </si>
-  <si>
-    <t>App验证手机号-企业号为空</t>
-  </si>
-  <si>
-    <t>{"QueryType": "checkUserPhone", "Params": '{"PHONE":"#USERPHONE#","ORGGUID": "", "AppName": "com.romens.health.pharmacy.client"}'}</t>
   </si>
   <si>
     <t>userLoginInByPwd</t>
@@ -836,7 +821,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr defaultRowHeight="15" baseColWidth="10"/>
   <cols>
     <col width="7.375" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -923,10 +908,10 @@
         <v>33</v>
       </c>
       <c r="G3" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="H3" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -937,7 +922,7 @@
         <v>29</v>
       </c>
       <c r="C4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>11</v>
@@ -946,10 +931,10 @@
         <v>12</v>
       </c>
       <c r="F4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G4" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="H4" t="s">
         <v>15</v>
@@ -963,7 +948,7 @@
         <v>29</v>
       </c>
       <c r="C5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>11</v>
@@ -972,10 +957,10 @@
         <v>12</v>
       </c>
       <c r="F5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G5" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="H5" t="s">
         <v>15</v>
@@ -989,7 +974,7 @@
         <v>29</v>
       </c>
       <c r="C6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>11</v>
@@ -998,65 +983,13 @@
         <v>12</v>
       </c>
       <c r="F6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G6" t="s">
         <v>26</v>
       </c>
       <c r="H6" t="s">
         <v>15</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9">
-      <c r="A7" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" t="s">
-        <v>29</v>
-      </c>
-      <c r="C7" t="s">
-        <v>41</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F7" t="s">
-        <v>42</v>
-      </c>
-      <c r="G7" t="s">
-        <v>26</v>
-      </c>
-      <c r="H7" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9">
-      <c r="A8" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" t="s">
-        <v>29</v>
-      </c>
-      <c r="C8" t="s">
-        <v>43</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F8" t="s">
-        <v>44</v>
-      </c>
-      <c r="G8" t="s">
-        <v>18</v>
-      </c>
-      <c r="H8" t="s">
-        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -1117,10 +1050,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="C2" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>11</v>
@@ -1129,7 +1062,7 @@
         <v>12</v>
       </c>
       <c r="F2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="G2" t="s">
         <v>14</v>
@@ -1143,10 +1076,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="C3" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>11</v>
@@ -1155,10 +1088,10 @@
         <v>12</v>
       </c>
       <c r="F3" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="G3" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="H3" t="s">
         <v>15</v>
@@ -1169,10 +1102,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="C4" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>11</v>
@@ -1181,10 +1114,10 @@
         <v>12</v>
       </c>
       <c r="F4" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="G4" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="H4" t="s">
         <v>15</v>
@@ -1195,10 +1128,10 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="C5" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>11</v>
@@ -1207,10 +1140,10 @@
         <v>12</v>
       </c>
       <c r="F5" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="G5" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="H5" t="s">
         <v>15</v>
@@ -1221,10 +1154,10 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="C6" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>11</v>
@@ -1233,7 +1166,7 @@
         <v>12</v>
       </c>
       <c r="F6" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="G6" t="s">
         <v>14</v>
@@ -1299,22 +1232,22 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="C2" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="D2" t="s">
         <v>11</v>
       </c>
       <c r="E2" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="F2" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="G2" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="H2" t="s">
         <v>15</v>
@@ -1325,22 +1258,22 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C3" t="s">
         <v>57</v>
       </c>
-      <c r="C3" t="s">
-        <v>62</v>
-      </c>
       <c r="D3" t="s">
         <v>11</v>
       </c>
       <c r="E3" t="s">
+        <v>54</v>
+      </c>
+      <c r="F3" t="s">
+        <v>58</v>
+      </c>
+      <c r="G3" t="s">
         <v>59</v>
-      </c>
-      <c r="F3" t="s">
-        <v>63</v>
-      </c>
-      <c r="G3" t="s">
-        <v>64</v>
       </c>
       <c r="H3" t="s">
         <v>15</v>
@@ -1351,22 +1284,22 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="C4" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="D4" t="s">
         <v>11</v>
       </c>
       <c r="E4" t="s">
+        <v>54</v>
+      </c>
+      <c r="F4" t="s">
+        <v>61</v>
+      </c>
+      <c r="G4" t="s">
         <v>59</v>
-      </c>
-      <c r="F4" t="s">
-        <v>66</v>
-      </c>
-      <c r="G4" t="s">
-        <v>64</v>
       </c>
       <c r="H4" t="s">
         <v>15</v>
@@ -1430,22 +1363,22 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="C2" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="D2" t="s">
         <v>11</v>
       </c>
       <c r="E2" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="F2" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="G2" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="H2" t="s">
         <v>15</v>
@@ -1456,22 +1389,22 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="C3" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="D3" t="s">
         <v>11</v>
       </c>
       <c r="E3" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="F3" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="G3" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="H3" t="s">
         <v>15</v>
@@ -1534,22 +1467,22 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="C2" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="D2" t="s">
         <v>11</v>
       </c>
       <c r="E2" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="F2" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="G2" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="H2" t="s">
         <v>15</v>
@@ -1560,22 +1493,22 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
+        <v>67</v>
+      </c>
+      <c r="C3" t="s">
+        <v>71</v>
+      </c>
+      <c r="D3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" t="s">
+        <v>54</v>
+      </c>
+      <c r="F3" t="s">
         <v>72</v>
       </c>
-      <c r="C3" t="s">
-        <v>76</v>
-      </c>
-      <c r="D3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E3" t="s">
-        <v>59</v>
-      </c>
-      <c r="F3" t="s">
-        <v>77</v>
-      </c>
       <c r="G3" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="H3" t="s">
         <v>15</v>
@@ -1638,22 +1571,22 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="C2" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="D2" t="s">
         <v>11</v>
       </c>
       <c r="E2" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="F2" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G2" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="H2" t="s">
         <v>15</v>
@@ -1714,22 +1647,22 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="C2" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="D2" t="s">
         <v>11</v>
       </c>
       <c r="E2" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="F2" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="G2" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="H2" t="s">
         <v>15</v>
@@ -1790,22 +1723,22 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="C2" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="D2" t="s">
         <v>11</v>
       </c>
       <c r="E2" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="F2" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="G2" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="H2" t="s">
         <v>15</v>

--- a/data/system.xlsx
+++ b/data/system.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="83">
   <si>
     <t>case_id</t>
   </si>
@@ -151,6 +151,9 @@
   </si>
   <si>
     <t>{"QueryType": "userLoginInByPwd", "Params": '{"DEVICEID":"#DEVICEID#","USERPHONE":"#USERPHONE#","PWD":"000000","ORGGUID":"#ORGGUID#","AppName":"com.romens.health.pharmacy.client"}'}</t>
+  </si>
+  <si>
+    <t>未通过</t>
   </si>
   <si>
     <t>App验证密码-密码为空</t>
@@ -1068,7 +1071,7 @@
         <v>14</v>
       </c>
       <c r="H2" t="s">
-        <v>15</v>
+        <v>43</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -1079,7 +1082,7 @@
         <v>40</v>
       </c>
       <c r="C3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>11</v>
@@ -1088,10 +1091,10 @@
         <v>12</v>
       </c>
       <c r="F3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H3" t="s">
         <v>15</v>
@@ -1105,7 +1108,7 @@
         <v>40</v>
       </c>
       <c r="C4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>11</v>
@@ -1114,10 +1117,10 @@
         <v>12</v>
       </c>
       <c r="F4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G4" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H4" t="s">
         <v>15</v>
@@ -1131,7 +1134,7 @@
         <v>40</v>
       </c>
       <c r="C5" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>11</v>
@@ -1140,10 +1143,10 @@
         <v>12</v>
       </c>
       <c r="F5" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H5" t="s">
         <v>15</v>
@@ -1157,7 +1160,7 @@
         <v>40</v>
       </c>
       <c r="C6" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>11</v>
@@ -1166,13 +1169,13 @@
         <v>12</v>
       </c>
       <c r="F6" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G6" t="s">
         <v>14</v>
       </c>
       <c r="H6" t="s">
-        <v>15</v>
+        <v>43</v>
       </c>
     </row>
   </sheetData>
@@ -1232,22 +1235,22 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D2" t="s">
         <v>11</v>
       </c>
       <c r="E2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H2" t="s">
         <v>15</v>
@@ -1258,22 +1261,22 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D3" t="s">
         <v>11</v>
       </c>
       <c r="E3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H3" t="s">
         <v>15</v>
@@ -1284,22 +1287,22 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C4" t="s">
+        <v>61</v>
+      </c>
+      <c r="D4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" t="s">
+        <v>55</v>
+      </c>
+      <c r="F4" t="s">
+        <v>62</v>
+      </c>
+      <c r="G4" t="s">
         <v>60</v>
-      </c>
-      <c r="D4" t="s">
-        <v>11</v>
-      </c>
-      <c r="E4" t="s">
-        <v>54</v>
-      </c>
-      <c r="F4" t="s">
-        <v>61</v>
-      </c>
-      <c r="G4" t="s">
-        <v>59</v>
       </c>
       <c r="H4" t="s">
         <v>15</v>
@@ -1363,22 +1366,22 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D2" t="s">
         <v>11</v>
       </c>
       <c r="E2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H2" t="s">
         <v>15</v>
@@ -1389,22 +1392,22 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D3" t="s">
         <v>11</v>
       </c>
       <c r="E3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H3" t="s">
         <v>15</v>
@@ -1467,22 +1470,22 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D2" t="s">
         <v>11</v>
       </c>
       <c r="E2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H2" t="s">
         <v>15</v>
@@ -1493,22 +1496,22 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C3" t="s">
+        <v>72</v>
+      </c>
+      <c r="D3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" t="s">
+        <v>55</v>
+      </c>
+      <c r="F3" t="s">
+        <v>73</v>
+      </c>
+      <c r="G3" t="s">
         <v>71</v>
-      </c>
-      <c r="D3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E3" t="s">
-        <v>54</v>
-      </c>
-      <c r="F3" t="s">
-        <v>72</v>
-      </c>
-      <c r="G3" t="s">
-        <v>70</v>
       </c>
       <c r="H3" t="s">
         <v>15</v>
@@ -1571,22 +1574,22 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D2" t="s">
         <v>11</v>
       </c>
       <c r="E2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H2" t="s">
         <v>15</v>
@@ -1647,22 +1650,22 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D2" t="s">
         <v>11</v>
       </c>
       <c r="E2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H2" t="s">
         <v>15</v>
@@ -1723,22 +1726,22 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D2" t="s">
         <v>11</v>
       </c>
       <c r="E2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H2" t="s">
         <v>15</v>
